--- a/public/uploads/project-docs/course-registration-planning.xlsx
+++ b/public/uploads/project-docs/course-registration-planning.xlsx
@@ -9134,7 +9134,7 @@
       </c>
       <c r="L7" s="791" t="inlineStr">
         <is>
-          <t>진행중</t>
+          <t>완료</t>
         </is>
       </c>
     </row>
